--- a/data/trans_dic/P55$privada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Provincia-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,49</t>
+          <t>0,0; 52,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,28</t>
+          <t>0,0; 47,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 20,21</t>
+          <t>2,52; 23,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,28</t>
+          <t>0,0; 57,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,96</t>
+          <t>0,0; 20,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,55</t>
+          <t>0,0; 30,69</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,27; 22,54</t>
+          <t>5,59; 22,02</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,12</t>
+          <t>0,0; 34,77</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 19,65</t>
+          <t>2,03; 19,58</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,54</t>
+          <t>0,0; 23,62</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,72; 17,77</t>
+          <t>4,76; 17,53</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 11,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,3</t>
+          <t>0,0; 26,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,55; 55,8</t>
+          <t>6,85; 56,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,87; 50,65</t>
+          <t>10,86; 50,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 33,27</t>
+          <t>3,93; 36,42</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 33,36</t>
+          <t>7,2; 34,2</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,85; 33,68</t>
+          <t>6,05; 32,01</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>10,49; 26,11</t>
+          <t>9,77; 25,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,28; 21,71</t>
+          <t>2,25; 21,07</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6,91; 26,07</t>
+          <t>7,35; 27,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,17; 34,29</t>
+          <t>8,6; 33,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,37; 27,02</t>
+          <t>12,28; 27,41</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,8</t>
+          <t>0,0; 53,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,61; 50,35</t>
+          <t>6,67; 54,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5,67; 50,68</t>
+          <t>8,36; 51,38</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,28; 26,64</t>
+          <t>6,08; 28,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>16,55; 47,25</t>
+          <t>15,83; 48,67</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,18; 36,81</t>
+          <t>4,19; 37,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,14</t>
+          <t>0,0; 37,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,48; 27,18</t>
+          <t>9,67; 26,16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,38; 44,2</t>
+          <t>16,35; 43,97</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,82; 32,5</t>
+          <t>7,72; 32,21</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,47; 35,88</t>
+          <t>6,67; 36,7</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,79; 23,95</t>
+          <t>10,56; 23,79</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,23</t>
+          <t>0,0; 32,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,09</t>
+          <t>0,0; 33,44</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,63; 45,53</t>
+          <t>5,55; 45,79</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,36; 41,36</t>
+          <t>9,84; 40,88</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,34; 41,88</t>
+          <t>11,82; 44,01</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,55; 23,08</t>
+          <t>2,64; 24,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,06; 41,32</t>
+          <t>7,07; 42,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,21; 32,92</t>
+          <t>15,47; 33,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,68; 33,32</t>
+          <t>9,46; 33,32</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,15; 23,18</t>
+          <t>5,13; 21,48</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,81; 37,49</t>
+          <t>9,32; 37,73</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,98; 31,26</t>
+          <t>15,89; 31,87</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,53</t>
+          <t>0,0; 49,88</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1287,52 +1287,52 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,13</t>
+          <t>0,0; 39,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,01</t>
+          <t>0,0; 29,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,81; 41,06</t>
+          <t>8,04; 41,41</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,22; 36,73</t>
+          <t>4,46; 34,98</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,16; 29,42</t>
+          <t>6,11; 28,96</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,71</t>
+          <t>0,0; 23,9</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 35,57</t>
+          <t>8,59; 34,26</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,72; 30,71</t>
+          <t>3,76; 30,56</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>5,91; 25,28</t>
+          <t>6,52; 24,86</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 43,92</t>
+          <t>5,37; 46,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,62</t>
+          <t>0,0; 35,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,82</t>
+          <t>0,0; 28,41</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,58; 30,94</t>
+          <t>10,47; 30,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,73</t>
+          <t>0,0; 27,52</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,11; 44,19</t>
+          <t>5,06; 39,99</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,93</t>
+          <t>0,0; 43,24</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7,91; 23,24</t>
+          <t>8,06; 23,03</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>6,11; 25,97</t>
+          <t>4,78; 26,04</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,49; 29,85</t>
+          <t>5,53; 29,67</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,25; 31,94</t>
+          <t>4,33; 30,64</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,12; 23,66</t>
+          <t>10,82; 23,36</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,51</t>
+          <t>0,0; 28,89</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,2; 38,97</t>
+          <t>7,15; 38,84</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,51; 32,77</t>
+          <t>6,47; 34,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,02; 24,25</t>
+          <t>3,09; 26,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>25,17; 55,96</t>
+          <t>24,47; 55,15</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,49; 43,59</t>
+          <t>14,05; 42,58</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,99; 29,41</t>
+          <t>8,03; 29,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,03; 27,23</t>
+          <t>10,19; 27,99</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>19,63; 43,77</t>
+          <t>18,26; 42,48</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14,88; 35,23</t>
+          <t>15,02; 37,3</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,08; 26,17</t>
+          <t>9,26; 26,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,52; 23,61</t>
+          <t>9,96; 24,08</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,89; 32,65</t>
+          <t>5,08; 31,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,11</t>
+          <t>0,0; 34,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,7</t>
+          <t>0,0; 21,42</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,25; 41,94</t>
+          <t>10,32; 41,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,38; 31,0</t>
+          <t>7,44; 31,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,1; 30,73</t>
+          <t>7,07; 30,42</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,16; 32,02</t>
+          <t>7,96; 31,71</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>16,08; 32,57</t>
+          <t>15,39; 31,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,66; 26,34</t>
+          <t>9,28; 27,48</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,65; 24,81</t>
+          <t>6,69; 25,62</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,42; 23,78</t>
+          <t>6,83; 24,69</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,54; 31,19</t>
+          <t>16,47; 30,39</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,32; 18,22</t>
+          <t>7,09; 18,0</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,3; 20,25</t>
+          <t>8,83; 20,67</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,49; 21,58</t>
+          <t>9,42; 21,43</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12,06; 20,57</t>
+          <t>11,88; 21,02</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,6; 27,85</t>
+          <t>16,67; 27,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,6; 21,9</t>
+          <t>12,45; 21,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,22; 21,93</t>
+          <t>11,48; 22,14</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,54; 21,52</t>
+          <t>15,33; 21,65</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,36; 22,51</t>
+          <t>14,56; 22,25</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,34; 20,02</t>
+          <t>12,48; 19,9</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,92; 20,04</t>
+          <t>11,69; 19,38</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,04; 20,29</t>
+          <t>15,28; 20,15</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales</t>
+          <t>Población a la que, al menos, tiene ayuda privada cuando tiene dificultades en la actividades instrumentales (tasa de respuesta: 98,48%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2209,62 +2209,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3684</t>
+          <t>0; 4561</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5569</t>
+          <t>0; 5603</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1412</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>677; 5463</t>
+          <t>681; 6383</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 4945</t>
+          <t>0; 5899</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 4254</t>
+          <t>0; 5722</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7319</t>
+          <t>0; 7599</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1734; 7413</t>
+          <t>1840; 7243</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6453</t>
+          <t>0; 6576</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>813; 7902</t>
+          <t>815; 7875</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7271</t>
+          <t>0; 7975</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2830; 10652</t>
+          <t>2855; 10506</t>
         </is>
       </c>
     </row>
@@ -2417,62 +2417,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 1926</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6657</t>
+          <t>0; 6298</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>961; 7106</t>
+          <t>872; 7187</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1673; 7791</t>
+          <t>1671; 7704</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>905; 7556</t>
+          <t>893; 8270</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3169; 14123</t>
+          <t>3049; 14477</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2125; 12239</t>
+          <t>2200; 11633</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5769; 14363</t>
+          <t>5373; 14147</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>887; 8465</t>
+          <t>877; 8215</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4550; 17169</t>
+          <t>4842; 18309</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4500; 16830</t>
+          <t>4223; 16203</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8706; 19021</t>
+          <t>8644; 19291</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4772</t>
+          <t>0; 5589</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>951; 7249</t>
+          <t>960; 7805</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>835; 7468</t>
+          <t>1232; 7572</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1356; 6840</t>
+          <t>1563; 7226</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5917; 16891</t>
+          <t>5657; 17399</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1108; 9751</t>
+          <t>1109; 9825</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6782</t>
+          <t>0; 6550</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>5114; 12103</t>
+          <t>4305; 11649</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7562; 20403</t>
+          <t>7548; 20299</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3199; 13289</t>
+          <t>3156; 13170</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2394; 11505</t>
+          <t>2139; 11766</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7577; 16819</t>
+          <t>7417; 16701</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4450</t>
+          <t>0; 4384</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 7530</t>
+          <t>0; 6442</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>785; 6355</t>
+          <t>774; 6392</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1714; 6843</t>
+          <t>1628; 6764</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3939; 13369</t>
+          <t>3774; 14049</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1005; 9110</t>
+          <t>1040; 9547</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2074; 12141</t>
+          <t>2077; 12418</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5462; 11824</t>
+          <t>5556; 11886</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4384; 15099</t>
+          <t>4285; 15097</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3023; 13613</t>
+          <t>3012; 12613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4250; 16249</t>
+          <t>4041; 16350</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8383; 16402</t>
+          <t>8337; 16721</t>
         </is>
       </c>
     </row>
@@ -3041,7 +3041,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 3934</t>
+          <t>0; 4309</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -3051,52 +3051,52 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 1303</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3128</t>
+          <t>0; 3194</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5155</t>
+          <t>0; 4576</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1973; 10371</t>
+          <t>2030; 10461</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1019; 8873</t>
+          <t>1078; 8450</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>995; 4747</t>
+          <t>986; 4672</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 6236</t>
+          <t>0; 5798</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2125; 12178</t>
+          <t>2941; 11729</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1083; 8934</t>
+          <t>1094; 8891</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1427; 6101</t>
+          <t>1573; 6000</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>964; 7891</t>
+          <t>965; 8442</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6440</t>
+          <t>0; 6447</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5051</t>
+          <t>0; 4244</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2560; 7485</t>
+          <t>2533; 7358</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6634</t>
+          <t>0; 7693</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1089; 9406</t>
+          <t>1077; 8510</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 9808</t>
+          <t>0; 10114</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2496; 7335</t>
+          <t>2544; 7270</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2805; 11928</t>
+          <t>2194; 11959</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2160; 11752</t>
+          <t>2177; 11679</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1630; 12241</t>
+          <t>1658; 11744</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6198; 13192</t>
+          <t>6034; 13022</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5710</t>
+          <t>0; 5406</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2112; 11429</t>
+          <t>2097; 11390</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1720; 8662</t>
+          <t>1711; 9066</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>701; 5637</t>
+          <t>718; 6141</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9860; 21923</t>
+          <t>9587; 21605</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>7154; 21518</t>
+          <t>6935; 21019</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4498; 16565</t>
+          <t>4523; 16824</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5360; 14551</t>
+          <t>5444; 14956</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>11362; 25338</t>
+          <t>10572; 24588</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11713; 27720</t>
+          <t>11820; 29353</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7517; 21654</t>
+          <t>7662; 21849</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7298; 18103</t>
+          <t>7641; 18468</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1913; 10610</t>
+          <t>1652; 10147</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 6479</t>
+          <t>0; 7092</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5121</t>
+          <t>0; 5299</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1743; 7130</t>
+          <t>1754; 7042</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3508; 14742</t>
+          <t>3538; 15216</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3329; 14409</t>
+          <t>3313; 14263</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4543; 17829</t>
+          <t>4434; 17651</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9451; 19139</t>
+          <t>9043; 18685</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7730; 21087</t>
+          <t>7428; 22000</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4504; 16799</t>
+          <t>4529; 17347</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5163; 19120</t>
+          <t>5492; 19854</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>12534; 23629</t>
+          <t>12473; 23023</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>9267; 23059</t>
+          <t>8978; 22788</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12129; 29601</t>
+          <t>12907; 30208</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11525; 26215</t>
+          <t>11444; 26023</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18949; 32316</t>
+          <t>18667; 33011</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>38331; 64313</t>
+          <t>38499; 63705</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>35222; 61208</t>
+          <t>34794; 61431</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30009; 58628</t>
+          <t>30705; 59190</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>51023; 70644</t>
+          <t>50322; 71059</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>51325; 80466</t>
+          <t>52046; 79541</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>52537; 85224</t>
+          <t>53131; 84693</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>46339; 77914</t>
+          <t>45469; 75345</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>72994; 98478</t>
+          <t>74166; 97772</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P55$privada-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P55$privada-Provincia-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>9,86%</t>
         </is>
       </c>
     </row>
@@ -717,12 +717,12 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,61</t>
+          <t>0,0; 42,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,57</t>
+          <t>0,0; 46,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -732,47 +732,47 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 23,61</t>
+          <t>2,33; 19,4</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 57,6</t>
+          <t>0,0; 47,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,12</t>
+          <t>0,0; 18,6</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,69</t>
+          <t>0,0; 27,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5,59; 22,02</t>
+          <t>4,96; 22,01</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,77</t>
+          <t>0,0; 31,81</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 19,58</t>
+          <t>2,02; 17,94</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,62</t>
+          <t>0,0; 22,27</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,53</t>
+          <t>4,99; 16,44</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,78%</t>
         </is>
       </c>
     </row>
@@ -862,57 +862,57 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,78</t>
+          <t>0,0; 28,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6,85; 56,44</t>
+          <t>7,97; 58,97</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10,86; 50,08</t>
+          <t>11,24; 52,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,93; 36,42</t>
+          <t>3,97; 33,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,2; 34,2</t>
+          <t>5,47; 34,04</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,05; 32,01</t>
+          <t>5,6; 33,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>9,77; 25,72</t>
+          <t>10,73; 25,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 21,07</t>
+          <t>2,36; 20,73</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7,35; 27,8</t>
+          <t>7,34; 27,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,6; 33,02</t>
+          <t>9,08; 32,03</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,28; 27,41</t>
+          <t>12,97; 28,47</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,86%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,64</t>
+          <t>0,0; 53,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 54,2</t>
+          <t>6,68; 47,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,36; 51,38</t>
+          <t>5,68; 51,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,08; 28,14</t>
+          <t>6,48; 27,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,83; 48,67</t>
+          <t>18,2; 49,72</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4,19; 37,09</t>
+          <t>8,09; 37,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,8</t>
+          <t>0,0; 38,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>9,67; 26,16</t>
+          <t>11,22; 27,82</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16,35; 43,97</t>
+          <t>15,28; 43,72</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7,72; 32,21</t>
+          <t>7,81; 32,51</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6,67; 36,7</t>
+          <t>7,51; 37,05</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,56; 23,79</t>
+          <t>11,16; 24,46</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>23,35%</t>
+          <t>23,06%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,85%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,74</t>
+          <t>0,0; 26,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,44</t>
+          <t>0,0; 34,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5,55; 45,79</t>
+          <t>5,51; 43,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 40,88</t>
+          <t>10,33; 40,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,82; 44,01</t>
+          <t>12,17; 41,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,64; 24,19</t>
+          <t>2,58; 22,99</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 42,27</t>
+          <t>7,4; 45,97</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>15,47; 33,09</t>
+          <t>15,38; 32,21</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,46; 33,32</t>
+          <t>10,07; 33,74</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5,13; 21,48</t>
+          <t>5,18; 21,59</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9,32; 37,73</t>
+          <t>9,47; 36,8</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,89; 31,87</t>
+          <t>15,75; 31,41</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,88</t>
+          <t>0,0; 45,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,74</t>
+          <t>0,0; 62,54</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,96</t>
+          <t>0,0; 39,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,3</t>
+          <t>0,0; 34,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,04; 41,41</t>
+          <t>7,81; 41,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 34,98</t>
+          <t>4,36; 34,05</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>6,11; 28,96</t>
+          <t>5,24; 28,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 23,9</t>
+          <t>0,0; 26,64</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8,59; 34,26</t>
+          <t>8,67; 34,61</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3,76; 30,56</t>
+          <t>3,77; 30,73</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,52; 24,86</t>
+          <t>6,86; 24,44</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,79%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,37; 46,98</t>
+          <t>10,32; 42,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,66</t>
+          <t>0,0; 35,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,41</t>
+          <t>0,0; 33,56</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>10,47; 30,42</t>
+          <t>10,27; 31,46</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,52</t>
+          <t>0,0; 24,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5,06; 39,99</t>
+          <t>5,08; 40,62</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,24</t>
+          <t>0,0; 39,0</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>8,06; 23,03</t>
+          <t>8,22; 23,37</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4,78; 26,04</t>
+          <t>6,17; 25,25</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>5,53; 29,67</t>
+          <t>5,46; 30,0</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4,33; 30,64</t>
+          <t>4,45; 30,25</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,82; 23,36</t>
+          <t>11,35; 23,7</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,89</t>
+          <t>0,0; 29,12</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,15; 38,84</t>
+          <t>7,09; 38,87</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,47; 34,3</t>
+          <t>6,55; 35,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3,09; 26,42</t>
+          <t>0,0; 26,5</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>24,47; 55,15</t>
+          <t>24,17; 56,26</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,05; 42,58</t>
+          <t>13,36; 42,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,03; 29,87</t>
+          <t>8,08; 28,7</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10,19; 27,99</t>
+          <t>10,13; 27,19</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,26; 42,48</t>
+          <t>18,88; 42,04</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15,02; 37,3</t>
+          <t>14,19; 36,5</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>9,26; 26,4</t>
+          <t>8,99; 26,23</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>9,96; 24,08</t>
+          <t>8,61; 22,48</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>23,22%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22,84%</t>
+          <t>23,02%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>5,08; 31,22</t>
+          <t>6,54; 33,39</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,05</t>
+          <t>0,0; 30,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,42</t>
+          <t>0,0; 21,77</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>10,32; 41,42</t>
+          <t>8,86; 38,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,44; 31,99</t>
+          <t>7,3; 30,5</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,07; 30,42</t>
+          <t>7,08; 28,66</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,96; 31,71</t>
+          <t>6,53; 31,43</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>15,39; 31,8</t>
+          <t>16,35; 33,39</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>9,28; 27,48</t>
+          <t>9,11; 27,3</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6,69; 25,62</t>
+          <t>6,57; 24,73</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6,83; 24,69</t>
+          <t>6,64; 24,0</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>16,47; 30,39</t>
+          <t>16,55; 32,77</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1824,7 +1824,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,59%</t>
         </is>
       </c>
     </row>
@@ -1837,62 +1837,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7,09; 18,0</t>
+          <t>7,1; 17,85</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>8,83; 20,67</t>
+          <t>8,83; 20,93</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9,42; 21,43</t>
+          <t>9,13; 21,11</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11,88; 21,02</t>
+          <t>11,83; 20,97</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>16,67; 27,59</t>
+          <t>16,56; 27,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12,45; 21,98</t>
+          <t>12,38; 21,52</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>11,48; 22,14</t>
+          <t>11,5; 21,35</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15,33; 21,65</t>
+          <t>15,5; 21,76</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>14,56; 22,25</t>
+          <t>14,77; 22,51</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12,48; 19,9</t>
+          <t>11,98; 19,56</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11,69; 19,38</t>
+          <t>11,91; 19,76</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>15,28; 20,15</t>
+          <t>15,13; 20,27</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2187</t>
+          <t>2117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3838</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>6025</t>
+          <t>6192</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 4561</t>
+          <t>0; 3645</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 5603</t>
+          <t>0; 5494</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -2224,47 +2224,47 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>681; 6383</t>
+          <t>680; 5672</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5899</t>
+          <t>0; 4856</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 5722</t>
+          <t>0; 5290</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7599</t>
+          <t>0; 6867</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1840; 7243</t>
+          <t>1667; 7394</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6576</t>
+          <t>0; 6015</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>815; 7875</t>
+          <t>811; 7214</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 7975</t>
+          <t>0; 7517</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2855; 10506</t>
+          <t>3132; 10331</t>
         </is>
       </c>
     </row>
@@ -2364,7 +2364,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4250</t>
+          <t>4668</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>9497</t>
+          <t>10163</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2404,7 +2404,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>13747</t>
+          <t>14832</t>
         </is>
       </c>
     </row>
@@ -2422,57 +2422,57 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6298</t>
+          <t>0; 6806</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>872; 7187</t>
+          <t>1015; 7509</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1671; 7704</t>
+          <t>1851; 8618</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>893; 8270</t>
+          <t>902; 7543</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3049; 14477</t>
+          <t>2316; 14410</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2200; 11633</t>
+          <t>2035; 12080</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5373; 14147</t>
+          <t>6279; 14840</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>877; 8215</t>
+          <t>921; 8082</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>4842; 18309</t>
+          <t>4834; 18212</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4223; 16203</t>
+          <t>4455; 15721</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>8644; 19291</t>
+          <t>9731; 21356</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3554</t>
+          <t>3575</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2592,7 +2592,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>7972</t>
+          <t>8196</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2612,7 +2612,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>11526</t>
+          <t>11770</t>
         </is>
       </c>
     </row>
@@ -2625,62 +2625,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5589</t>
+          <t>0; 5563</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>960; 7805</t>
+          <t>961; 6792</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1232; 7572</t>
+          <t>836; 7533</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1563; 7226</t>
+          <t>1634; 6925</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5657; 17399</t>
+          <t>6506; 17773</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1109; 9825</t>
+          <t>2144; 9826</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 6550</t>
+          <t>0; 6613</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>4305; 11649</t>
+          <t>5005; 12408</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7548; 20299</t>
+          <t>7054; 20183</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3156; 13170</t>
+          <t>3193; 13292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>2139; 11766</t>
+          <t>2409; 11881</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>7417; 16701</t>
+          <t>7794; 17078</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3668</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2800,7 +2800,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8388</t>
+          <t>8761</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2820,7 +2820,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>12056</t>
+          <t>12735</t>
         </is>
       </c>
     </row>
@@ -2833,62 +2833,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4384</t>
+          <t>0; 3508</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6442</t>
+          <t>0; 6571</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>774; 6392</t>
+          <t>768; 6046</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1628; 6764</t>
+          <t>1835; 7202</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3774; 14049</t>
+          <t>3883; 13204</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1040; 9547</t>
+          <t>1017; 9072</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2077; 12418</t>
+          <t>2174; 13505</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5556; 11886</t>
+          <t>5844; 12236</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4285; 15097</t>
+          <t>4562; 15287</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>3012; 12613</t>
+          <t>3040; 12680</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4041; 16350</t>
+          <t>4102; 15948</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>8337; 16721</t>
+          <t>8780; 17509</t>
         </is>
       </c>
     </row>
@@ -2988,7 +2988,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1081</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2343</t>
+          <t>2438</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3424</t>
+          <t>3536</t>
         </is>
       </c>
     </row>
@@ -3041,12 +3041,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 4309</t>
+          <t>0; 3947</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 5541</t>
+          <t>0; 5613</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -3056,47 +3056,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 3194</t>
+          <t>0; 3268</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4576</t>
+          <t>0; 5360</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2030; 10461</t>
+          <t>1972; 10426</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1078; 8450</t>
+          <t>1053; 8225</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>986; 4672</t>
+          <t>880; 4767</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5798</t>
+          <t>0; 6463</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2941; 11729</t>
+          <t>2969; 11851</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1094; 8891</t>
+          <t>1095; 8938</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1573; 6000</t>
+          <t>1716; 6111</t>
         </is>
       </c>
     </row>
@@ -3196,7 +3196,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4675</t>
+          <t>4755</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3236,7 +3236,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>9230</t>
+          <t>9328</t>
         </is>
       </c>
     </row>
@@ -3249,62 +3249,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>965; 8442</t>
+          <t>1855; 7642</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 6447</t>
+          <t>0; 6470</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4244</t>
+          <t>0; 5012</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>2533; 7358</t>
+          <t>2488; 7622</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7693</t>
+          <t>0; 6938</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>1077; 8510</t>
+          <t>1082; 8644</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0; 10114</t>
+          <t>0; 9122</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2544; 7270</t>
+          <t>2641; 7513</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>2194; 11959</t>
+          <t>2835; 11595</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2177; 11679</t>
+          <t>2151; 11811</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1658; 11744</t>
+          <t>1705; 11592</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6034; 13022</t>
+          <t>6397; 13359</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>2258</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3424,7 +3424,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>9640</t>
+          <t>11060</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>11898</t>
+          <t>13978</t>
         </is>
       </c>
     </row>
@@ -3457,62 +3457,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 5406</t>
+          <t>0; 5449</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>2097; 11390</t>
+          <t>2078; 11399</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1711; 9066</t>
+          <t>1731; 9359</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>718; 6141</t>
+          <t>0; 7576</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>9587; 21605</t>
+          <t>9468; 22040</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6935; 21019</t>
+          <t>6595; 21141</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4523; 16824</t>
+          <t>4552; 16165</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>5444; 14956</t>
+          <t>6613; 17750</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>10572; 24588</t>
+          <t>10929; 24336</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>11820; 29353</t>
+          <t>11169; 28720</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>7662; 21849</t>
+          <t>7437; 21705</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7641; 18468</t>
+          <t>8085; 21102</t>
         </is>
       </c>
     </row>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>3658</t>
+          <t>4068</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>13645</t>
+          <t>16131</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>20199</t>
         </is>
       </c>
     </row>
@@ -3665,62 +3665,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1652; 10147</t>
+          <t>2126; 10853</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0; 7092</t>
+          <t>0; 6270</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0; 5299</t>
+          <t>0; 5386</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>1754; 7042</t>
+          <t>1721; 7513</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>3538; 15216</t>
+          <t>3470; 14505</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3313; 14263</t>
+          <t>3320; 13438</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>4434; 17651</t>
+          <t>3637; 17497</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>9043; 18685</t>
+          <t>11170; 22806</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>7428; 22000</t>
+          <t>7291; 21859</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>4529; 17347</t>
+          <t>4446; 16746</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5492; 19854</t>
+          <t>5339; 19301</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>12473; 23023</t>
+          <t>14521; 28754</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>25211</t>
+          <t>26992</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>60000</t>
+          <t>65579</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>85211</t>
+          <t>92571</t>
         </is>
       </c>
     </row>
@@ -3873,62 +3873,62 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>8978; 22788</t>
+          <t>8993; 22591</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>12907; 30208</t>
+          <t>12905; 30593</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>11444; 26023</t>
+          <t>11091; 25643</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>18667; 33011</t>
+          <t>20002; 35469</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>38499; 63705</t>
+          <t>38243; 63953</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>34794; 61431</t>
+          <t>34608; 60147</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>30705; 59190</t>
+          <t>30741; 57077</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>50322; 71059</t>
+          <t>55390; 77733</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>52046; 79541</t>
+          <t>52795; 80466</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>53131; 84693</t>
+          <t>50978; 83270</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45469; 75345</t>
+          <t>46327; 76812</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>74166; 97772</t>
+          <t>79630; 106687</t>
         </is>
       </c>
     </row>
